--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -522,6 +522,753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Pass YDs</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Rush YDs</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Rec YDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>TDs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sacks</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Flag Pulls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Malik Kurdi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>QB/ATH</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Omar Shaibe</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Yousef Shaibe</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hamzah Shaibe</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Ali Shaibe</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Sami Salama</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Moe Aburmishan</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TE/DB</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Rick Naser</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Hamzah Qreini</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Abdelqader</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>TE/OL/DL</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Yazan Aburmishan</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Ali Aburmishan</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ibraheem Aburmishan</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Yahya Ghouleh</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Omar Almallah</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Aedan Abdelqader</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Abdellah Farook</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>ATH/K</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -597,792 +1344,6 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Malik Kurdi</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>QB/ATH</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Omar Shaibe</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>WR/S</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Yousef Shaibe</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>WR/S</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Hamzah Shaibe</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Ali Shaibe</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Sami Salama</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>WR/S</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Moe Aburmishan</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Rick Naser</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Hamzah Qreini</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Ahmad Abdelqader</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Yazan Aburmishan</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>WR/S</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Ali Aburmishan</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ibraheem Aburmishan</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Yahya Ghouleh</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Omar Almallah</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Adean Abdelqader</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>OL/DL</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Abdellah Farook</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Sal Ahmed</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DL/LB</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>POS</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Pass YDs</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Rush YDs</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>REC</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Rec YDs</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>TDs</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sacks</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Flag Pulls</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1933,7 +1894,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mostafa El-leboudi</t>
+          <t>Mostafa El-Leboudi</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1963,6 +1924,123 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Shafiq Said</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WR/DB</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Ashkar</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>OL/DL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alowaid</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1255,6 +1255,45 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Sal Ahmad</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DL/LB</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -522,20 +522,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,40 +562,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -631,6 +667,24 @@
         <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -672,6 +726,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -711,6 +783,24 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -750,6 +840,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -789,6 +897,24 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -828,6 +954,24 @@
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -867,6 +1011,24 @@
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -906,6 +1068,24 @@
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -945,6 +1125,24 @@
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -984,6 +1182,24 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1023,6 +1239,24 @@
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1062,6 +1296,24 @@
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1101,6 +1353,24 @@
       <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1140,6 +1410,24 @@
       <c r="K15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1179,6 +1467,24 @@
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1218,6 +1524,24 @@
       <c r="K17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1257,6 +1581,24 @@
       <c r="K18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1294,6 +1636,24 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1308,20 +1668,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1342,40 +1708,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1419,6 +1815,24 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1458,6 +1872,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1497,6 +1929,24 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1536,6 +1986,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1575,6 +2043,24 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1614,6 +2100,24 @@
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1653,6 +2157,24 @@
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1692,6 +2214,24 @@
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1731,6 +2271,24 @@
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1770,6 +2328,24 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1809,6 +2385,24 @@
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1848,6 +2442,24 @@
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1885,6 +2497,24 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1926,6 +2556,24 @@
       <c r="K15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1965,6 +2613,24 @@
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2004,6 +2670,24 @@
       <c r="K17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2043,6 +2727,24 @@
       <c r="K18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2080,6 +2782,24 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -617,15 +617,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -685,6 +690,9 @@
         <v>0</v>
       </c>
       <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,6 +752,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -801,6 +812,9 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -858,6 +872,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -915,6 +932,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -972,6 +992,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1029,6 +1052,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1086,6 +1112,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1143,6 +1172,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1200,6 +1232,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1257,6 +1292,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1314,6 +1352,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1371,6 +1412,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1428,6 +1472,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1485,6 +1532,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1542,6 +1592,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1599,6 +1652,9 @@
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1654,6 +1710,9 @@
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1685,7 +1744,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1763,15 +1822,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1833,6 +1897,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1890,6 +1957,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1947,6 +2017,9 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -2004,6 +2077,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2061,6 +2137,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2118,6 +2197,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2175,6 +2257,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2232,6 +2317,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2289,6 +2377,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2346,6 +2437,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2403,6 +2497,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2460,6 +2557,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2515,6 +2615,9 @@
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2574,6 +2677,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2631,6 +2737,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2688,6 +2797,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2745,6 +2857,9 @@
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2800,6 +2915,9 @@
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
@@ -597,40 +597,45 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Rush TD</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Def TDs</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -693,6 +698,9 @@
         <v>0</v>
       </c>
       <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -755,6 +763,9 @@
       <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -815,6 +826,9 @@
       <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -875,6 +889,9 @@
       <c r="R5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -935,6 +952,9 @@
       <c r="R6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -995,6 +1015,9 @@
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1055,6 +1078,9 @@
       <c r="R8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1115,6 +1141,9 @@
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1175,6 +1204,9 @@
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1235,6 +1267,9 @@
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1295,6 +1330,9 @@
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1355,6 +1393,9 @@
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1415,6 +1456,9 @@
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1475,6 +1519,9 @@
       <c r="R15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1535,6 +1582,9 @@
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1595,6 +1645,9 @@
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1655,6 +1708,9 @@
       <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1713,6 +1769,9 @@
         <v>0</v>
       </c>
       <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1727,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1740,7 +1799,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
@@ -1802,40 +1861,45 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Rush TD</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Def TDs</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1900,6 +1964,9 @@
       <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1960,6 +2027,9 @@
       <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2020,6 +2090,9 @@
       <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -2080,6 +2153,9 @@
       <c r="R5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2140,6 +2216,9 @@
       <c r="R6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2200,6 +2279,9 @@
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2260,6 +2342,9 @@
       <c r="R8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2320,6 +2405,9 @@
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2380,6 +2468,9 @@
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2440,6 +2531,9 @@
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2500,6 +2594,9 @@
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2560,6 +2657,9 @@
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2618,6 +2718,9 @@
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2680,6 +2783,9 @@
       <c r="R15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2740,6 +2846,9 @@
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2800,6 +2909,9 @@
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2860,6 +2972,9 @@
       <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2918,6 +3033,9 @@
         <v>0</v>
       </c>
       <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -1786,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3039,6 +3039,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Moe Ashkar</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>OL</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
+++ b/game-stats/Week6_WarBred_vs_Desert-Lions.xlsx
@@ -1786,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3102,6 +3102,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>No Name</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
